--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T17:58:44.896Z</t>
+    <t>2026-09-17T04:38:38.695Z</t>
   </si>
   <si>
     <t>Open Trading Account Online &amp; Invest in Stock, MF, IPO &amp; More with HDFC Securities</t>
